--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importXmslContractList.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importXmslContractList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\25757\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fushudong\workspace20230814\opmp\Ft-Cloud\ft-services\ft-service-pm\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{571CD90A-608F-4AB0-B700-A221580992C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C9D092-567F-45B5-A623-7E85B3BCD729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2023-07-05" sheetId="1" r:id="rId1"/>
@@ -20,88 +20,51 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
-  <si>
-    <t>层级码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>父层级码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>清单编号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>清单中文名称</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>清单外文名称</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>清单类型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>单位</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>中标数量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>中标单价（不含税）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>中标金额（不含税）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>变更数量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>变更单价（不含税）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>变更金额（不含税）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>变更后数量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>变更后单价（不含税）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>变更后金额（不含税）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -115,12 +78,6 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -176,23 +133,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -470,27 +421,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="2" width="16.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" customWidth="1"/>
-    <col min="4" max="4" width="16.5546875" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="19.6640625" customWidth="1"/>
-    <col min="8" max="8" width="17.21875" customWidth="1"/>
-    <col min="9" max="9" width="20.44140625" customWidth="1"/>
-    <col min="10" max="10" width="23.5546875" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
-    <col min="12" max="12" width="24.44140625" customWidth="1"/>
-    <col min="13" max="13" width="20.33203125" customWidth="1"/>
-    <col min="14" max="14" width="18.44140625" customWidth="1"/>
-    <col min="15" max="15" width="22.33203125" customWidth="1"/>
-    <col min="16" max="16" width="20.21875" customWidth="1"/>
+    <col min="1" max="1" width="15.125" customWidth="1"/>
+    <col min="2" max="2" width="16.5" customWidth="1"/>
+    <col min="3" max="3" width="17.375" customWidth="1"/>
+    <col min="4" max="4" width="11.375" customWidth="1"/>
+    <col min="5" max="5" width="19.625" customWidth="1"/>
+    <col min="6" max="6" width="17.25" customWidth="1"/>
+    <col min="7" max="7" width="20.5" customWidth="1"/>
+    <col min="8" max="8" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -515,51 +459,20 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
     </row>
-    <row r="2" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="5"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="5"/>
+      <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="G2" s="3"/>
       <c r="H2" s="2"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importXmslContractList.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importXmslContractList.xlsx
@@ -8,14 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fushudong\workspace20230814\opmp\Ft-Cloud\ft-services\ft-service-pm\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C9D092-567F-45B5-A623-7E85B3BCD729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B6E505F-C06E-41BB-ABB9-A9BEE831D5C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2023-07-05" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -468,10 +477,26 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="2"/>
+      <c r="H2" s="2">
+        <f>F2*G2</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="3">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F1048576" xr:uid="{15C1DB12-A8C4-4019-8D51-2546CEE637C0}">
+      <formula1>0</formula1>
+      <formula2>99999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576" xr:uid="{B5769CB8-45AD-41D2-A396-BC0474DD8511}">
+      <formula1>0</formula1>
+      <formula2>999999999</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576" xr:uid="{0AFF8616-4E56-4336-97CE-306705D593ED}">
+      <formula1>"普通清单,计日工,暂定金,10%不可预见费"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importXmslContractList.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importXmslContractList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fushudong\workspace20230814\opmp\Ft-Cloud\ft-services\ft-service-pm\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B6E505F-C06E-41BB-ABB9-A9BEE831D5C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D741089-FEF2-42DD-8E11-A711940C0E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>清单编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -60,6 +60,30 @@
   </si>
   <si>
     <t>中标金额（不含税）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>层级码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-1-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2-2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -142,7 +166,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -153,6 +177,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -430,71 +463,108 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="15.125" customWidth="1"/>
-    <col min="2" max="2" width="16.5" customWidth="1"/>
-    <col min="3" max="3" width="17.375" customWidth="1"/>
-    <col min="4" max="4" width="11.375" customWidth="1"/>
-    <col min="5" max="5" width="19.625" customWidth="1"/>
-    <col min="6" max="6" width="17.25" customWidth="1"/>
-    <col min="7" max="7" width="20.5" customWidth="1"/>
-    <col min="8" max="8" width="23.5" customWidth="1"/>
+    <col min="1" max="1" width="9" style="5"/>
+    <col min="2" max="2" width="15.125" customWidth="1"/>
+    <col min="3" max="3" width="16.5" customWidth="1"/>
+    <col min="4" max="4" width="17.375" customWidth="1"/>
+    <col min="5" max="5" width="11.375" customWidth="1"/>
+    <col min="6" max="6" width="19.625" customWidth="1"/>
+    <col min="7" max="7" width="17.25" customWidth="1"/>
+    <col min="8" max="8" width="20.5" customWidth="1"/>
+    <col min="9" max="9" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="3"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="2"/>
+    <row r="2" spans="1:9" ht="13.9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="3"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="2">
-        <f>F2*G2</f>
+      <c r="G2" s="2"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="2">
+        <f>G2*H2</f>
         <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A3" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A4" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A5" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A6" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A7" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="3">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F1048576" xr:uid="{15C1DB12-A8C4-4019-8D51-2546CEE637C0}">
-      <formula1>0</formula1>
-      <formula2>99999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576" xr:uid="{B5769CB8-45AD-41D2-A396-BC0474DD8511}">
+  <dataValidations count="5">
+    <dataValidation type="whole" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576" xr:uid="{15C1DB12-A8C4-4019-8D51-2546CEE637C0}">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576" xr:uid="{0AFF8616-4E56-4336-97CE-306705D593ED}">
+    <dataValidation type="decimal" showInputMessage="1" showErrorMessage="1" sqref="H1:H1048576" xr:uid="{B5769CB8-45AD-41D2-A396-BC0474DD8511}">
+      <formula1>0</formula1>
+      <formula2>999999999</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{0AFF8616-4E56-4336-97CE-306705D593ED}">
       <formula1>"普通清单,计日工,暂定金,10%不可预见费"</formula1>
+    </dataValidation>
+    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{8C7B18EB-1706-4693-9E43-8A9FE2C13F13}"/>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I1048576" xr:uid="{FE5B1BE9-5258-40AE-9D5E-942ABC6FCDE2}">
+      <formula1>0</formula1>
+      <formula2>999999999</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
